--- a/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-Beneficiary.xlsx
+++ b/tiflow/audit-event-profile/2.0.0-ballot.2/StructureDefinition-GEM-ERP-EX-Beneficiary.xlsx
@@ -1335,7 +1335,7 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>109</v>
